--- a/dp_阶段1/data1.xlsx
+++ b/dp_阶段1/data1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,920 +458,2300 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>张若昀棉花娃娃20cmq版明星同人可爱周边玩偶礼物送朋友闺蜜【3月20日发完】</t>
+          <t>爱豆应援定制明星明信片爱豆周边满天星手辐方形手幅</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-08-12/2b8cccc7-e630-48d0-848d-3b29e28bb9af.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-01-10/664e5b11-9981-4ace-9e69-753ff5012415.jpeg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2740</v>
+        <v>571</v>
       </c>
       <c r="D2" t="n">
-        <v>3850</v>
+        <v>900</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=794704429188</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=889148715108</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>张若昀周边2025全年/2025跨年周历日历台历生日礼物桌面摆件定制</t>
+          <t>2026春晚张若昀亲笔签名照6寸明星周边亲签保真应援福利宣传礼物</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/open-gw/2024-10-19/18226524-7ed9-4937-ab19-e3c32f46ffc8.jpeg</t>
+          <t>https://img.pddpic.com/mms-goods-image/2026-02-20/ceb82084-82ec-4941-a21f-e50dc6512710.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3000</v>
+        <v>527</v>
       </c>
       <c r="D3" t="n">
-        <v>3600</v>
+        <v>1888</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=661236575231</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=906118494247</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>张若昀明星Q版陶瓷马克杯早餐勺子情侣咖啡茶杯办公水杯礼物</t>
+          <t>亚克力钥匙扣立牌摇摇乐定制明星周边挂件校园礼品摆件人物人型图</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-07-01/502752f3-56c9-4c51-b163-f28eefcd9986.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-12-14/827b7d21-7a2b-4546-85e7-242dd6026cde.jpeg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>490</v>
+        <v>2388</v>
       </c>
       <c r="D4" t="n">
-        <v>1090</v>
+        <v>2930</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=628999589052</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=692266705865</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>张若昀周边按动中性笔学生考试刷题专用0.5mm顺滑速干高颜值黑笔</t>
+          <t>张若昀发声吧唧语音钥匙扣周边可充电女生生日礼物发完</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-06-13/cfdaa637-de47-4313-9873-2ef896bd4eba.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-12-22/07aa8f54-826c-437b-9457-99b1f4e14e07.jpeg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>2200</v>
       </c>
       <c r="D5" t="n">
-        <v>421</v>
+        <v>2500</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=761490520863</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=877121607306</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>张若昀周边同款保温杯明星生日礼物送女生应援不锈钢咖啡喝水杯子</t>
+          <t>明星张若昀小身份证保护套挡脸防磁套信息遮挡头套</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-10-18/9795ef05-9eb0-412b-8a06-d6b694785f3e.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-09-16/de54e259-8660-4ffd-a8b2-daddad852a1a.png.a.jpeg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3200</v>
+        <v>159</v>
       </c>
       <c r="D6" t="n">
-        <v>3600</v>
+        <v>1500</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=839031024913</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=819444597321</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>张若昀高颜值316咖啡保温杯男女学生办公随行便捷手提吸管杯</t>
+          <t>异形票根来图定制双面小卡书签门票演唱会明星周边应援满天星亮膜【7天内发货】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/open-gw/2025-09-29/8913a63584667b9d43ae71d9943cb182.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-06-10/3e8ea8ae-dc0f-4b55-8507-562a7f7d35fb.jpeg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2090</v>
+        <v>1450</v>
       </c>
       <c r="D7" t="n">
-        <v>2490</v>
+        <v>1595</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=828238838293</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=622194465891</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>张若昀属性20cm棉花娃娃明星同人可爱周边玩偶礼物送朋友闺蜜礼物【3月29日发完】</t>
+          <t>来图定制双开门pp夹抖音小红书同款亚克力双开门pp夹明星物料定制</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-09-11/dff7bbe8-f7c2-4628-a61c-87b5dc6dbf7e.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-12-09/345c452a-f996-471e-9dd8-161e76b5ad29.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2720</v>
+        <v>494</v>
       </c>
       <c r="D8" t="n">
-        <v>5159</v>
+        <v>656</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=815707334303</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=869505206202</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>张若昀2025年精装语录台历</t>
+          <t>人之初张若昀亲笔签名照 周边应援礼 剧宣6寸明信片 明星亲签保真</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/open-gw/2024-11-25/8576865a-6fab-4570-8c78-1db7036cf3e8.jpeg</t>
+          <t>https://img.pddpic.com/mms-goods-image/2025-12-31/e2b6222e-246b-4d83-b0fe-9e2e26f780b2.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3462</v>
+        <v>753</v>
       </c>
       <c r="D9" t="n">
-        <v>4104</v>
+        <v>2433</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=676667318690</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=883124637289</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>庆余年张若昀范闲周边抱枕沙发靠垫子宿舍午睡靠背毛绒小枕头摆件</t>
+          <t>张若昀 小卡爱豆吧唧徽章拍立得镭射票周边礼物书签套装福袋生日</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-10-15/ae504406-fb4a-45c1-a48b-036df4ad3e48.jpeg</t>
+          <t>https://img.pddpic.com/open-gw/2025-06-06/511da5e1-3cd6-4127-ba30-b4662856bcc4.jpeg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="D10" t="n">
-        <v>690</v>
+        <v>1090</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=659825684471</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=758254544269</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>张若昀周边桌面相框摆件灯光画镜子卧室床头画diy生日礼物送女生</t>
+          <t>PVC透卡定制小卡方卡透明卡来图定做动漫应援明星周边演唱会ins风【5天内发货】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-11-06/91fddc8e-19d0-45d0-ba18-0b257dad7e10.jpeg</t>
+          <t>https://img.pddpic.com/goods_mms/2025-08-08/99b9bd5b-9ff1-4363-92d5-81bc8f2b2a38.jpeg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>280</v>
+        <v>1090</v>
       </c>
       <c r="D11" t="n">
-        <v>2160</v>
+        <v>1200</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=668404567104</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=751358886581</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>张若昀周边同款保温杯明星生日礼物送女生应援不锈钢咖啡喝水杯子</t>
+          <t>张若昀随心配周边饭制数量感小卡明信片小方卡书签高颜值超值便宜</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/open-gw/2025-09-25/62f797fb-ce35-4c07-8899-3c5afa151414.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-07-19/af813994-fa16-4c06-bdc1-efb76992e73f.jpeg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2580</v>
+        <v>890</v>
       </c>
       <c r="D12" t="n">
-        <v>3080</v>
+        <v>1419</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=825647598757</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=633609342470</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>张若昀明星周边学生随身便携折叠镜化妆镜迷你补妆镜宿舍梳妆镜女</t>
+          <t>【张若昀】2023GQ濮院活动媒体宣发卡整套,带官封全新放心买</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-09-20/8b04551c-b2ac-4b16-a461-996f18d7ba72.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-03-20/cdcaacee-0b10-4300-b046-483fb6c7828f.jpeg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>168</v>
+        <v>3520</v>
       </c>
       <c r="D13" t="n">
-        <v>1280</v>
+        <v>4939</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=651972093845</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=719770152311</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>张若昀属性20cm棉花娃娃明星同人可爱周边玩偶礼物送朋友生日礼物【3月29日发完】</t>
+          <t>张若昀织布周边应援包包挂件装饰行李箱明星应援周边书包挂饰</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-09-11/2a96a729-5ede-487f-b215-c414f3be6a73.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-12-15/45f41ff0-4adc-4f92-9346-e8c44a2f4f7b.jpeg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2720</v>
+        <v>365</v>
       </c>
       <c r="D14" t="n">
-        <v>5379</v>
+        <v>788</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=797342979879</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=684738890609</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>张若昀周边笔盒学生大容量帆布铅笔袋文具盒明星同款粉丝应援礼物</t>
+          <t>亚克力随身镜钥匙扣挂件来图定制明星应援创意化妆镜diy小镜子</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-10-12/7847435e-d6c7-42c9-906d-699fbb26bb1c.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-05-01/5dd1bca6-3d9e-49c3-93f5-4668d62fc4e6.jpeg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1383</v>
+        <v>192</v>
       </c>
       <c r="D15" t="n">
-        <v>2080</v>
+        <v>500</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=835202111100</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=611718691476</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>张若昀周边小挂表可爱学生考试专用静音走时可挂可立送朋友闺蜜表</t>
+          <t>张若昀亚克力钥匙扣潮流时尚书包行李箱挂件精选新品挂件明星款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-06-13/4ff160a6-8644-44d5-a035-8251417bb215.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-03-01/337f31a0-54c7-47ac-9385-055461f7e650.jpeg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>99</v>
+        <v>380</v>
       </c>
       <c r="D16" t="n">
-        <v>466</v>
+        <v>900</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=761492466644</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=710715564934</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>张若昀新款2025-2026年双年台历写真学生桌面摆件双面日历明星</t>
+          <t>『三寸特惠』大陆明星张若昀 保真亲笔签名海报照3寸卡钻送礼现货</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-07-03/ec59bce7-92ee-4ffa-b3f9-be371faf2969.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-09-16/e3bdc7e3-5427-49ec-a012-eca29059df0e.jpeg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1280</v>
+        <v>2720</v>
       </c>
       <c r="D17" t="n">
-        <v>2380</v>
+        <v>5368</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=772536020670</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=819657072634</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>范闲抱枕庆余年2电视剧周边枕头张若昀明星定制靠枕靠垫生日礼物</t>
+          <t>张若昀督促学习禁止偷懒禁止摆烂亚克力桌面立牌摆件钥匙扣挂件</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-06-03/2d4d92dc-ac0e-48d3-815c-312b6b724ed6.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-03-06/27627ea8-cfc7-4e16-ad71-0b3d450e47a0.jpeg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="D18" t="n">
-        <v>1490</v>
+        <v>431</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=620021278802</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=847497438299</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>张若昀2026双面语录台历照片明星定制新款摆件桌面diy日历创意</t>
+          <t>定制自印镭射uv逆向闪卡明星/动漫周边定制硬卡明星应援双闪小卡【15天内发货】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-09-18/45a79303-5d5d-47ba-8c29-825ac4764fd1.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-10-12/3a4835ae-c885-4b04-bf36-b33003c804ba.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3010</v>
+        <v>1400</v>
       </c>
       <c r="D19" t="n">
-        <v>4389</v>
+        <v>2000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=821030921451</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=658859133830</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>张若昀2026周历创意简约台历桌面摆台周边小清新活页日历记事本</t>
+          <t>张若昀去学习立牌庆余年同款钥匙扣桌面摆件送闺蜜生日礼物新款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-10-18/15275735-1068-4286-b871-ac6eb952f9fd.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-05-24/5d7c3049-1a6e-4977-82eb-72a27e60b814.png</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3100</v>
+        <v>296</v>
       </c>
       <c r="D20" t="n">
-        <v>3800</v>
+        <v>471</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=660934283953</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=632912196860</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>张若昀吧唧58mm收藏8K+痛包徽章胸针马口铁谷子明星应援演唱会</t>
+          <t>张若昀抽象搞笑老鼠干内置铁丝搞怪可任意造型周边应援抽象玩偶【3月16日发完】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-08-08/7cbbba90-e974-41c2-b1fd-3f7d9260d895.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2026-01-29/64af9ca5-ec2f-4f2a-aebc-55da71e01faf.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>799</v>
       </c>
       <c r="D21" t="n">
-        <v>890</v>
+        <v>1699</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=792284640030</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=901411434578</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>张若昀 日历台历2026年照片写真摆台现货应援周边生日礼品物8寸A5</t>
+          <t>张若昀成品应援姓名牌可爱生日礼物不织布蓝色毛绒应援可爱挂饰【3月16日发完】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-06-27/6a029d2b-21fd-49fe-8f44-595b00c2a858.png.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2026-01-06/94e8c437-e686-4b09-baac-d7181c547274.png.a.jpeg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2080</v>
+        <v>540</v>
       </c>
       <c r="D22" t="n">
-        <v>2480</v>
+        <v>700</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=769026442698</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=886720267774</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>张若昀周边同款卧室小夜灯相框摆件生日礼物送女生粉丝应援灯光画</t>
+          <t>130张张若昀帅气高颜值男明星明星贴纸周边手机手账防水装饰贴画</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-08-21/20e87380-6609-4fbd-ac76-2abde1820c7f.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-06-16/bab080cb-6a48-43b5-be21-45593b8d7333.png.a.jpeg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2490</v>
+        <v>143</v>
       </c>
       <c r="D23" t="n">
-        <v>2890</v>
+        <v>1500</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=800201033836</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=762985665389</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>张若昀周边新款2026年台历创意简约桌面月历周历日历送生日礼物</t>
+          <t>【保真】明星张若昀亲笔签名照3寸宣传照送闺蜜礼物送朋友现货</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-12-05/46efb3cb-027d-4205-abb1-4e7592424c15.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-09-19/418e1817-d74e-4a42-b02b-aef9d8425e8e.jpeg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1880</v>
+        <v>1164</v>
       </c>
       <c r="D24" t="n">
-        <v>2580</v>
+        <v>7480</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=867100229692</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=821678201294</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>张若昀抱枕明星周边抱枕同款床上长枕头生日礼物人形玩偶靠枕</t>
+          <t>张若昀周边应援物料手幅小卡明信片ins风高颜值礼品杂志便宜包邮</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-08-25/016eff2c-ffdb-4d60-891b-6e655429cd99.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-05-08/918443d7-28ca-4a73-a334-2875ae05a2ae.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>688</v>
+        <v>1010</v>
       </c>
       <c r="D25" t="n">
-        <v>6600</v>
+        <v>1890</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=802771120765</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=744410322609</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>张若昀庆余年范闲属性闲豆包棉花娃娃明星小说周边超可爱同人努努</t>
+          <t>张若昀属性20cm棉花娃娃明星同人可爱周边玩偶礼物送朋友闺蜜【3月22日发完】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-09-13/bf299a3b-7630-4249-be5e-9df07525ea88.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-08-13/1667a4ca-a448-445b-8970-8f78c1606d41.jpeg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3190</v>
+        <v>2820</v>
       </c>
       <c r="D26" t="n">
-        <v>4950</v>
+        <v>4939</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=817294988428</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=795291735146</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>张若昀本子定制周边日记本a5活页本手账本学生文具笔记本朋友礼物</t>
+          <t>张若昀签名手链张若昀同款手链惊蛰庆余年主演范闲张若昀应援手链</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-08-08/9b345654-0172-4ca8-aa17-289b8e759c6b.jpeg.a.jpeg</t>
+          <t>https://t00img.yangkeduo.com/goods/images/2019-12-04/4c555e80-e5c2-4a5b-86c7-e1a15c0b1726.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>280</v>
+        <v>490</v>
       </c>
       <c r="D27" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=792386787198</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=72481976107</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>张若昀周边书签定制照应援学生文具闺蜜生日收藏纪念朋友节日礼物</t>
+          <t>张若昀抽纸袋包包挂件高颜值同款男明星表情包演员粉丝抽象搞怪【3月20日发完】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/open-gw/2025-04-15/571d97a2-05e9-4215-9da2-8715e038de5d.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-11-29/dd5626e1-93b4-461e-9f96-be6058aba150.jpeg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1880</v>
+        <v>599</v>
       </c>
       <c r="D28" t="n">
-        <v>2354</v>
+        <v>1499</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=733287115567</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=863548386309</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>张若昀罗云熙应援棒周边保温杯带吸管咖啡杯不锈钢随手杯便携ins【3月17日发完】</t>
+          <t>计入销量 Man About Town 城市画报杂志2025年11月 张若昀A/B封面【60天内发货】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-goods-image/2025-10-28/d900a985-2c34-4436-a6d4-07556c02fb1e.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-goods-image/2025-12-03/6f3e435b-db2c-40f6-8103-fd9ffe23ee94.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1080</v>
+        <v>5500</v>
       </c>
       <c r="D29" t="n">
-        <v>3080</v>
+        <v>6000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=845251044093</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=861087016593</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>张若昀周边新款2026年台历创意简约桌面月历周历日历送生日礼物</t>
+          <t>张若昀饭制周边全套覆膜小卡数量感高颜值书签明信片方卡送精美装</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-12-05/647a543f-8559-44bc-9323-c13d17a1d24e.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-08-10/7ee8e9c1-35d9-44fa-a127-428613fd77d2.jpeg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1880</v>
+        <v>990</v>
       </c>
       <c r="D30" t="n">
-        <v>2580</v>
+        <v>1557</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=867094760141</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=793388258197</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>张若昀周边周历2026年同款日历桌面摆台小卡水晶相框新年礼物</t>
+          <t>张若昀周边小挂表可爱学生考试专用静音走时可挂可立送朋友闺蜜表</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-goods-image/2026-02-04/db779b24-6be6-47bc-a718-4302a66ba784.png.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-06-13/4ff160a6-8644-44d5-a035-8251417bb215.jpeg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1480</v>
+        <v>399</v>
       </c>
       <c r="D31" t="n">
-        <v>2400</v>
+        <v>466</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=903865545784</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=761492466644</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>张若昀应援周边戒指昀朵昀哥大昀肖像生日签名简约不掉色爆款指环</t>
+          <t>【原创正版】张若昀发声吧唧语音钥匙扣周边可发声送女生生日礼物【9天内发货】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-05-18/8172269a-a4cb-4ee3-acb2-dbcf805f8c79.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2026-01-07/c55d9fe4-5553-470d-a60c-3f4adda306e4.jpeg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>366</v>
+        <v>2450</v>
       </c>
       <c r="D32" t="n">
-        <v>1590</v>
+        <v>2695</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=615974272257</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=863945739630</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>张若昀周边应援手机链庆余年周边挂件挂绳背包装饰礼物送朋友范闲</t>
+          <t>自印小卡明星卡片周边爱豆应援明信片纸质双面方卡印刷来图定制</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-08-13/4804560a-b534-4a70-9f65-21b3459412ad.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-12-09/7d85b200-1985-4e01-8d9b-90931e128e06.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>289</v>
+        <v>1432</v>
       </c>
       <c r="D33" t="n">
-        <v>889</v>
+        <v>2500</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=795025455368</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=674521724625</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>庆余年张若昀范闲高颜值水晶相框送朋友个性装饰摆件卧室高档摆台</t>
+          <t>9.9张若昀超值同款覆膜小卡书签明信片最新应援物立牌吧唧赠送数</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2024-05-28/210c72b2-8d3f-4c71-9e0a-9d1bf500cabd.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-10-23/3347202f-968d-414b-b249-ae9c19b4b1e0.jpeg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>431</v>
+        <v>578</v>
       </c>
       <c r="D34" t="n">
-        <v>2080</v>
+        <v>690</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=618419184313</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=662739181051</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>张若昀实力宝藏明星老鼠干内置铁丝骨架可任意造型玩偶应援周边【3月16日发完】</t>
+          <t>张若昀饭制周边同人眼睛光栅可动高颜值绝美COS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-goods-image/2025-11-25/110858bc-97e2-4289-ac0b-a39466692746.png.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-04-16/b2754fdc-6259-42d6-ba42-08555604e5ef.jpeg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>459</v>
+        <v>990</v>
       </c>
       <c r="D35" t="n">
-        <v>1699</v>
+        <v>1639</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=861025248788</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=733854880812</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>张若昀帅气高清照片粉丝应援小众摆件新款卧室宿舍木质相框摆台</t>
+          <t>张若昀2026春晚拍立得收纳盒饭制DIY纪念礼小卡双面镭射自制ins</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-goods-image/2025-12-07/a239eb08-ff1c-4b65-8fe3-530e52b81ec5.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-goods-image/2026-02-19/6bf269cf-b293-4e38-9782-d4be415a1033.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>392</v>
       </c>
       <c r="D36" t="n">
-        <v>1400</v>
+        <v>499</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=868397030162</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=906006032377</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>张若昀台历2026年日历新款月历高颜值动漫卡通相框摆台钥匙扣礼物</t>
+          <t>中国32届光之来金鹰节 张若昀收藏典藏卡牌小卡</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-goods-image/2025-09-08/46c8e5d8-de45-4303-929e-e9267fdfd42d.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2026-02-03/9ed7ce6d-2125-4de2-96f8-d348cc16c40f.jpeg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1480</v>
+        <v>748</v>
       </c>
       <c r="D37" t="n">
-        <v>2400</v>
+        <v>880</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=895485214687</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=903426667386</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>张若昀原创棉花娃娃毛绒明星公仔多昀玩偶新款节日礼物现货热销</t>
+          <t>张若昀半身姓名牌应援周边织布挂件钥匙扣庆余年包包挂饰</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/open-gw/2024-10-05/b0388f66-00aa-4614-ae10-04bb34dd6022.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-10-18/8c003524-5521-4711-94e0-f3e0884fd29f.jpeg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5200</v>
+        <v>1193</v>
       </c>
       <c r="D38" t="n">
-        <v>5940</v>
+        <v>2959</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=656393145837</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=838822728737</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>张若昀从21世纪安全撤离周边海报照片来图定制超厚笔记A5胶套本</t>
+          <t>计入销量【张若昀封面+精彩内页】芭莎男士BAZAAR杂志2024年8月</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-02-24/5278c696-1806-4bf1-9827-556cbf0dfaa9.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2025-07-16/59d470fa-f27d-42b1-b226-cc0c935ce97b.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>264</v>
+        <v>1620</v>
       </c>
       <c r="D39" t="n">
-        <v>1280</v>
+        <v>3900</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=708176963441</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=780612129505</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>张若昀周边水晶玻璃相框摆台个性定制照片毕业礼物送同学生日礼物</t>
+          <t>张若昀闪卡剧名照6变闪卡庆余年周边3d光栅卡纪念礼物ins风小卡</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://img.pddpic.com/mms-material-img/2025-07-17/6cabe514-31e1-4b2f-9a3d-de02bd93fce7.jpeg.a.jpeg</t>
+          <t>https://img.pddpic.com/mms-material-img/2024-09-15/3707bb9e-3d13-48a5-8176-03fa01a6ca7a.jpeg.a.jpeg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>144</v>
+        <v>1013</v>
       </c>
       <c r="D40" t="n">
-        <v>950</v>
+        <v>2100</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://mobile.yangkeduo.com/goods.html?goods_id=781058747656</t>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=650480603221</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>张若昀原创定制便签便利贴可粘贴75mm饭制周边50页便携正方形桌面【3月11日发完】</t>
+          <t>张若昀2026年双年台历日历周边明星专辑写真照同款装饰摆台摆件礼</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>https://img.pddpic.com/mms-goods-image/2025-12-01/0d3d539f-08fb-42b9-a111-7897fcaf0035.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>980</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=864692706158</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>张若昀镭射小卡盒装覆膜高清纸质卡片明星周边照片圆角小卡写真</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-02-27/eb16e6f6-7222-4328-a1ea-9311d56102ec.jpeg</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>355</v>
+      </c>
+      <c r="D42" t="n">
+        <v>660</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=590483836714</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>张若昀微博语录卡张若昀周边lomo创意明信片张若昀照片</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2022-11-01/ffe1ccd5-63ee-4f75-b358-01b81757324f.png</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>848</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=427588582138</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>张若昀随心配9.9饭制周边应援物全套set小卡方卡书签明信片精致</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-10-18/61e941bc-cc6e-4dd3-bdfb-3d1dbf2383ce.jpeg</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>790</v>
+      </c>
+      <c r="D44" t="n">
+        <v>890</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=660903093614</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>张若昀周边可动眼睛条效果绝美光栅卡正版追星礼物</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-04-12/2ef9e586-14dc-41b2-a9a5-6088567a2d4b.jpeg</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1419</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=731887254741</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026春节晚会张若昀亲笔签名照保真应援亲笔签名鉴定证书限量春晚</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2026-02-18/ba1c1df6-fc52-4b91-97f4-9c86d88ca9e8.jpeg</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5287</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9777</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=905933411415</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【张若昀】2023GQ濮院活动媒体宣发卡,实拍实发,不退不换</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-03-12/85fe39b5-5ff9-4e56-8769-358b9d13079e.jpeg</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>12300</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16368</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=716001977074</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>现货 人之初 陈宇 张若昀主演同名电视剧原著小说</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2026-01-24/c13cf880-85b6-4906-a838-2c6664e9853b.jpeg</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1490</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1804</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=894047208644</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>张若昀拍立得小卡自印贺卡书签富士高清ins风diy全套手工便宜爱豆</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-07-19/e4fdb20d-16dd-4cf5-b759-34a9b0733b03.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=633826660855</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>张若昀吧唧58mm收藏8K+痛包徽章胸针马口铁谷子明星应援演唱会</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-08-08/7cbbba90-e974-41c2-b1fd-3f7d9260d895.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>199</v>
+      </c>
+      <c r="D50" t="n">
+        <v>890</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=792284640030</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【张若昀官周】脆升升正版明信片一套两张带原装信封官方正品周边</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-07-17/014d664b-eda6-4feb-9a8c-9bf489c4d1eb.jpeg</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2790</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3069</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=781171130165</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>张若昀周边镭射小卡圆角LOMO卡55张一盒爆米花卡膜明星衍生礼品</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-11-02/ee4ce30e-9c24-48cf-b149-a4ac71baaa6a.jpeg</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>296</v>
+      </c>
+      <c r="D52" t="n">
+        <v>520</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=666801826201</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>55张明星张若昀精致小卡片高颜LOMO生日礼物限量版珍藏卡卡册卡膜【4月3日发完】</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-goods-image/2025-08-27/75bcde88-de00-4edc-800a-43ad5f6059eb.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>296</v>
+      </c>
+      <c r="D53" t="n">
+        <v>496</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=804672102401</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【张若昀】2023年GQ活动的宣发卡集合整套9张,全新实拍实发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-12-06/969d6d39-40cf-46ef-be9b-6c5f484953b6.jpeg</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>15800</v>
+      </c>
+      <c r="D54" t="n">
+        <v>19789</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=867623785689</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>张若昀应援大旗定做定制旗帜户外演唱会音乐节手持制定明星</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-10-08/1c94685f-be5c-4a29-876a-8d09944b69ff.jpeg</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>490</v>
+      </c>
+      <c r="D55" t="n">
+        <v>310</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=832562648220</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>张若昀权威亚克力修正带超高颜值涂改透明改错大容量学生考试专用</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-06-15/5096fd90-ef81-4b10-8f29-c5433ffe1a2a.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>254</v>
+      </c>
+      <c r="D56" t="n">
+        <v>700</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=762825816500</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>张若昀原创定制便签便利贴可粘贴75mm饭制周边50页便携正方形桌面</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>https://img.pddpic.com/mms-material-img/2024-10-22/c8379371-c72a-426c-bc85-2bc6e03c3c1c.jpeg</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>90</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="C57" t="n">
+        <v>390</v>
+      </c>
+      <c r="D57" t="n">
         <v>490</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>https://mobile.yangkeduo.com/goods.html?goods_id=662095447988</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>张若昀周边明星同款小夜灯摆件高级感生日礼物送女生闺蜜粉丝应援</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-04-11/e911ca4c-c097-4b75-b53a-66c6a36a5e75.jpeg</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2790</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2890</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=731331998518</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>张若昀周边高清镭射圆角小卡约55张1盒lomo卡明星周边精美礼品</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-11-02/e5dbdd1d-b7ec-4284-a3bc-0670ff492a3b.jpeg</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>297</v>
+      </c>
+      <c r="D59" t="n">
+        <v>520</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=666764611437</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>张若昀数量感饭制随心配名侦探庆余年覆膜小卡下单赠送小礼品9.9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-06-20/413236db-3bc4-4d16-87d2-c49fa3256a80.jpeg</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>689</v>
+      </c>
+      <c r="D60" t="n">
+        <v>790</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=625422985746</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>张若昀数量感随心配应援物立牌吧唧正版小卡覆膜明信片最新全套</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-10-18/62f8c61c-0939-46c6-b70e-25e2964334f7.jpeg</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>590</v>
+      </c>
+      <c r="D61" t="n">
+        <v>690</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=660904131335</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>庆余年2周边新款张若昀范闲徽章自印明星谷子吧唧胸针挂件马口铁</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-06-05/9fdc593d-9d0a-48ab-8ffb-e12e1ba9f2db.jpeg</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>200</v>
+      </c>
+      <c r="D62" t="n">
+        <v>626</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=620895851639</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>范闲张若昀海报挂画庆余年第二季2明星周边宿舍卧室免打孔装饰画</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-09-02/867e4401-80b9-4a85-b77b-9b46c6c3db62.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>327</v>
+      </c>
+      <c r="D63" t="n">
+        <v>650</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=808834475798</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>『保真』明星张若昀 亲笔签名定妆照3寸1款送礼物收藏应援周边</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-08-22/333634a3-71b2-468a-8a2e-94dbe9d6f5e5.jpeg</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2108</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7568</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=800798248794</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>张若昀魔改棒超亮应援棒演唱会改棒定制荧光棒应援打call</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-08-06/63a8ee7b-e96b-45cd-a01d-574efe887766.jpeg</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3490</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3839</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=791075567565</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>张若昀权威亚克力按动中性笔高颜值学生写字考试专用刷题速干黑笔</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-05-21/8b5221b9-cbc5-48bf-a40d-4b791cac0f13.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>388</v>
+      </c>
+      <c r="D66" t="n">
+        <v>800</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=751000272201</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>张若昀微博之夜周边手幅小卡明信片ins风精致自制满天星大礼包</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-01-16/e8d800f1-26aa-4b14-92fa-9c841c705e79.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1899</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=697560308217</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>张若昀本子定制周边日记本a5活页本手账本学生文具笔记本朋友礼物</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-08-08/9b345654-0172-4ca8-aa17-289b8e759c6b.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>580</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=792386787198</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>张若昀应援周边戒指昀朵昀哥大昀肖像生日签名简约不掉色爆款指环</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-05-18/8172269a-a4cb-4ee3-acb2-dbcf805f8c79.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>666</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1590</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=615974272257</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>张若昀封面杂志8本装】时尚芭莎/睿士/精品/男人风尚/智族杂志</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-goods-image/2026-03-02/3884559c-fc3c-46a0-8f9d-08fc49164f12.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=849818961704</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【充电站原创】张若昀范闲古风set小卡15明信片2书签1应援物周边【7天内发货】</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-06-30/f92549ea-3824-49e4-a5d9-a86c6b5449fb.jpeg</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>570</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=624833154079</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>张若昀蓝蓝星光15件套全套满天星小卡票根明信片自制珍藏限量版</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/open-gw/2025-10-12/ce1b13c20e50bc41074074c84b15bcdc.jpeg</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>880</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=835372740182</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>金属签名贴纸 张若昀 明星亲笔签名笔记本手机转印贴纸</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/open-gw/2024-11-13/48a86322-c060-4b23-96ae-93505c98e2b9.jpeg</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>490</v>
+      </c>
+      <c r="D73" t="n">
+        <v>590</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=671505428239</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>新款张若昀Q版人物转印贴微立体防水贴diy装饰手机壳水杯周边贴纸</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-10-27/b7c8c912-c76a-496f-9a11-4bdd6a8b414f.png.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>399</v>
+      </c>
+      <c r="D74" t="n">
+        <v>599</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=844576445536</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【24小时发货】随心配饭制张若昀小卡含亚克力数量感值周边小礼物</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-04-16/7fcf8188-d7c6-4b84-a20e-3a7f3604128a.jpeg</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>690</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1309</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=733787282485</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>张若昀高颜值316咖啡保温杯男女学生办公随行便捷车载手提吸管杯</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/open-gw/2025-09-29/8913a63584667b9d43ae71d9943cb182.jpeg</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=844498290611</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>张若昀庆余年2周边小卡范闲同款拍立得签名杂志3寸明信片lomo卡片</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-12-26/405cf551-38aa-4257-9503-0b33b37e01a9.jpeg</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>398</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=689117095990</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>小芒集卡社大侦探第九季【张若昀】永久珍藏卡牌SSR卡位</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-09-05/645ee68d-c27d-4905-aa45-ce47593cfa1c.jpeg</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>732</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=811061244054</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>张若昀周边徽章吧唧周边58mm马口铁胸章胸针挂件朋友生日礼物</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-12-16/22a02cf9-e8e9-4441-b496-72fe0b4778f5.png.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>266</v>
+      </c>
+      <c r="D79" t="n">
+        <v>390</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=873788948329</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【张若昀/封面】智族杂志张若昀GQ 2022年7月 正品清仓时尚</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-02-13/afa9846e-e54f-4b64-a0fe-ecba33987639.png</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1780</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=702927952083</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>64枚张若昀贴纸帅气精美高颜值范闲徐凤年高清周边装饰创意diy</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/open-gw/2025-08-09/ccf38e9b-15f3-4b1b-b6d8-1164dce18b06.jpeg</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>264</v>
+      </c>
+      <c r="D81" t="n">
+        <v>498</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=792708560194</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>张若昀高颜值周边亚克力书包行李箱挂件钥匙扣饰品学生节日礼物</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-goods-image/2025-09-22/cd49b0fb-900a-45fe-9416-8840984bfac2.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>331</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=823290499485</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>张若昀织布全世界周边应援包包挂件装饰行李箱文字书包钥匙扣挂饰</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-12-15/8d118949-fe43-4e8d-a7d7-4839e91c46eb.jpeg</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>365</v>
+      </c>
+      <c r="D83" t="n">
+        <v>788</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=684740573739</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>张若昀督促学习禁止偷懒禁止摆烂亚克力桌面立牌摆件钥匙扣定制</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-03-06/1b24244f-db31-4946-b695-37008adde510.jpeg</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>480</v>
+      </c>
+      <c r="D84" t="n">
+        <v>880</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=713203861698</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>张若昀从21世纪安全撤离周边自创八件套满天星手幅小卡明信片应援</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-07-20/a79d9d91-c3b5-4504-b06e-b82937ce05b5.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1231</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1690</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=633987405764</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>张若昀亚克力周边钥匙扣创意学生书包挂件吊坠装饰明星粉丝应援礼</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-goods-image/2025-12-06/b777b2b0-bb86-4c71-9fef-371c22acec75.png.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>320</v>
+      </c>
+      <c r="D86" t="n">
+        <v>920</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=867868536303</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>张若昀周边镭射高颜小卡3寸圆角LOMO卡小卡55张一盒精美礼品</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-05-18/e58071e1-59a7-4c0a-88fc-4b17cf7c510c.jpeg</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>387</v>
+      </c>
+      <c r="D87" t="n">
+        <v>300</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=615895554738</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>庆余年3寸珠光小卡张若昀范闲李沁陈道明付辛博毛晓彤金晨宋轶</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/open-gw/2024-06-17/298ed368-70ca-4adc-812c-e6a2b138e8ec.jpeg</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>810</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=624232542994</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>张若昀亲笔签名照 张若昀同款亲签周边保真无印刷6寸礼物送朋友</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-05-23/4164be5f-1de7-45bd-871d-1558f82a17da.jpeg</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>272</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=616950778730</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>【原创】张若昀 粉丝见面会Q版立牌钥匙扣PP夹</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/open-gw/2025-01-27/debefeb2-64b1-41aa-ade6-9fbc29f21152.jpeg</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>405</v>
+      </c>
+      <c r="D90" t="n">
+        <v>550</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=699369947373</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>张若昀张张包小卡正版正品张若昀小卡大侦探卡张若昀最新小卡明星</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-04-08/8aa45644-94a3-47f1-a448-79f713d8f1a7.jpeg</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>850</v>
+      </c>
+      <c r="D91" t="n">
+        <v>950</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=728990891142</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【充电站原创】张若昀范闲古风set小卡15明信片2书签1应援物周边【7天内发货】</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-06-01/c0214695-da84-44b9-a6cf-29e20dd49e68.jpeg</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>690</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=619511452136</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>张若昀三寸镭射小卡50张不重复自印送人高清卡片盒装LOMO明信片</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-03-01/7e8cd8b8-0f0b-408e-a32a-ceaa9de9f059.jpeg</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>356</v>
+      </c>
+      <c r="D93" t="n">
+        <v>628</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=591477188602</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>最新张若昀双面高清炫彩镭射票纪念书签全套送卡膜应援必备礼物</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-goods-image/2025-11-24/b5e1fef8-6631-4d67-8932-3abf86bd5fb5.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>298</v>
+      </c>
+      <c r="D94" t="n">
+        <v>790</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=861194899706</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>自制双面明星张若昀周边亚克力书法笔袋照片书包挂件钥匙扣配饰</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-10-18/3afaf375-9e2c-43a8-83cd-8ddac90bf441.jpeg</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>430</v>
+      </c>
+      <c r="D95" t="n">
+        <v>530</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=839240540957</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>明星周边张若昀手机壳适用苹果小米荣耀华为红米真我vivoOPPO一加</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-goods-image/2025-08-28/0c8edf51-22ac-431b-8422-258e645ab435.jpeg.a.jpeg</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>499</v>
+      </c>
+      <c r="D96" t="n">
+        <v>599</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=805401861994</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>张若昀督促学习禁止偷懒禁止摆烂亚克力桌面立牌摆件钥匙扣挂件</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-03-06/5575b14a-7d98-49d5-b0d1-ea5fac7df846.jpeg</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>520</v>
+      </c>
+      <c r="D97" t="n">
+        <v>720</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=713107558388</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>张若昀9.9饭制周边随心配set小卡方卡书签明信片名侦探最新立牌</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-10-23/571cd51e-7600-4f5f-aa49-4bf7be3a2e4a.jpeg</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>790</v>
+      </c>
+      <c r="D98" t="n">
+        <v>890</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=662845928793</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>张若昀手机链原创设计应援色小挂件挂链演唱会周边闺蜜礼物</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2026-01-09/ae7f3d5f-b862-4e44-abed-e6ce7407e9ce.jpeg</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>968</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2288</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=888554046402</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>庆余年张若昀亲笔签名照时尚周边保真非印刷应援粉丝福利爆款</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2024-12-23/dc2910f5-d775-4a74-aa15-a72ca2480be3.jpeg</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>960</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=688210841558</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>内娱明星张若昀亲笔签名照全套礼盒带机构认证送朋友粉丝礼物</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://img.pddpic.com/mms-material-img/2025-11-25/f84b38f7-b57e-4acb-916a-8b69eec7726c.jpeg</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>8670</v>
+      </c>
+      <c r="D101" t="n">
+        <v>16280</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://mobile.yangkeduo.com/goods.html?goods_id=860908965977</t>
         </is>
       </c>
     </row>
